--- a/reviews/a-envoyer/pierre-huiban-2026-10-12.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-12.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05T11:25:16</t>
+          <t>2026-10-05T13:13:54</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>388275035</v>
+        <v>388533906</v>
       </c>
       <c r="C6" t="n">
         <v>6572293</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>388275068</v>
+        <v>388533933</v>
       </c>
       <c r="C7" t="n">
         <v>6572293</v>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>388275094</v>
+        <v>388533960</v>
       </c>
       <c r="C9" t="n">
         <v>6572293</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>388275125</v>
+        <v>388534037</v>
       </c>
       <c r="C11" t="n">
         <v>6572293</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>388275156</v>
+        <v>388534059</v>
       </c>
       <c r="C13" t="n">
         <v>6572293</v>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>388275303</v>
+        <v>388534428</v>
       </c>
       <c r="C14" t="n">
         <v>6572293</v>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>388275330</v>
+        <v>388534444</v>
       </c>
       <c r="C15" t="n">
         <v>6572293</v>

--- a/reviews/a-envoyer/pierre-huiban-2026-10-12.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-12.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05T13:13:54</t>
+          <t>2026-10-09T06:15:40</t>
         </is>
       </c>
     </row>

--- a/reviews/a-envoyer/pierre-huiban-2026-10-12.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-12.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09T06:15:40</t>
+          <t>2026-10-09T11:44:29</t>
         </is>
       </c>
     </row>
